--- a/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0001T0006Z000C1N44_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0001T0006Z000C1N44_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>36.98011022612715</v>
+        <v>6.009267911745662</v>
       </c>
       <c r="D2" t="n">
-        <v>36.96619324125766</v>
+        <v>6.007006401704369</v>
       </c>
       <c r="E2" t="n">
-        <v>9.392262286698234</v>
+        <v>1.526242621588463</v>
       </c>
       <c r="F2" t="n">
-        <v>9.395453525878906</v>
+        <v>1.526761197955323</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>41.78357897720412</v>
+        <v>6.789831583795669</v>
       </c>
       <c r="D3" t="n">
-        <v>41.77493156497708</v>
+        <v>6.788426379308776</v>
       </c>
       <c r="E3" t="n">
-        <v>9.392262286698234</v>
+        <v>1.526242621588463</v>
       </c>
       <c r="F3" t="n">
-        <v>9.395453525878906</v>
+        <v>1.526761197955323</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>48.07370626282343</v>
+        <v>7.811977267708808</v>
       </c>
       <c r="D4" t="n">
-        <v>48.06804902287659</v>
+        <v>7.811057966217446</v>
       </c>
       <c r="E4" t="n">
-        <v>9.392262286698234</v>
+        <v>1.526242621588463</v>
       </c>
       <c r="F4" t="n">
-        <v>9.395453525878906</v>
+        <v>1.526761197955323</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>34.83639662874075</v>
+        <v>5.660914452170372</v>
       </c>
       <c r="D5" t="n">
-        <v>34.82330799127862</v>
+        <v>5.658787548582776</v>
       </c>
       <c r="E5" t="n">
-        <v>9.392262286698234</v>
+        <v>1.526242621588463</v>
       </c>
       <c r="F5" t="n">
-        <v>9.395453525878906</v>
+        <v>1.526761197955323</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>18.4893552357395</v>
+        <v>3.004520225807668</v>
       </c>
       <c r="D6" t="n">
-        <v>18.47524030401385</v>
+        <v>3.002226549402251</v>
       </c>
       <c r="E6" t="n">
-        <v>9.392262286698234</v>
+        <v>1.526242621588463</v>
       </c>
       <c r="F6" t="n">
-        <v>9.395453525878906</v>
+        <v>1.526761197955323</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>55.30214883343367</v>
+        <v>8.986599185432972</v>
       </c>
       <c r="D7" t="n">
-        <v>55.30819121808376</v>
+        <v>8.98758107293861</v>
       </c>
       <c r="E7" t="n">
-        <v>9.392262286698234</v>
+        <v>1.526242621588463</v>
       </c>
       <c r="F7" t="n">
-        <v>9.395453525878906</v>
+        <v>1.526761197955323</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>35.21535944419855</v>
+        <v>5.722495909682265</v>
       </c>
       <c r="D8" t="n">
-        <v>35.21829926464304</v>
+        <v>5.722973630504494</v>
       </c>
       <c r="E8" t="n">
-        <v>9.392262286698234</v>
+        <v>1.526242621588463</v>
       </c>
       <c r="F8" t="n">
-        <v>9.395453525878906</v>
+        <v>1.526761197955323</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>36.83152663721326</v>
+        <v>5.985123078547154</v>
       </c>
       <c r="D9" t="n">
-        <v>36.84522942712838</v>
+        <v>5.987349781908362</v>
       </c>
       <c r="E9" t="n">
-        <v>9.392262286698234</v>
+        <v>1.526242621588463</v>
       </c>
       <c r="F9" t="n">
-        <v>9.395453525878906</v>
+        <v>1.526761197955323</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>30.80354979992532</v>
+        <v>5.005576842487865</v>
       </c>
       <c r="D10" t="n">
-        <v>30.81414824260544</v>
+        <v>5.007299089423385</v>
       </c>
       <c r="E10" t="n">
-        <v>9.392262286698234</v>
+        <v>1.526242621588463</v>
       </c>
       <c r="F10" t="n">
-        <v>9.395453525878906</v>
+        <v>1.526761197955323</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>41.79016873672604</v>
+        <v>6.790902419717981</v>
       </c>
       <c r="D11" t="n">
-        <v>41.80434445688693</v>
+        <v>6.793205974244127</v>
       </c>
       <c r="E11" t="n">
-        <v>9.392262286698234</v>
+        <v>1.526242621588463</v>
       </c>
       <c r="F11" t="n">
-        <v>9.395453525878906</v>
+        <v>1.526761197955323</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
